--- a/data/dividends_info_20260731.xlsx
+++ b/data/dividends_info_20260731.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>47.06000137329102</v>
+        <v>45.67499923706055</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1912452132886669</v>
+        <v>0.1970443382667302</v>
       </c>
       <c r="J2" t="n">
         <v>227</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>66</v>
+        <v>65.34999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.060606060606061</v>
+        <v>1.071155342531803</v>
       </c>
       <c r="J3" t="n">
         <v>206</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.020000457763672</v>
+        <v>9.199999809265137</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6651884363083036</v>
+        <v>0.6521739265643809</v>
       </c>
       <c r="J4" t="n">
         <v>136</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>47.06000137329102</v>
+        <v>45.67499923706055</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1912452132886669</v>
+        <v>0.1970443382667302</v>
       </c>
       <c r="J6" t="n">
         <v>136</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.109999895095825</v>
+        <v>2.099999904632568</v>
       </c>
       <c r="I7" t="n">
-        <v>3.649289280960038</v>
+        <v>3.666666833181238</v>
       </c>
       <c r="J7" t="n">
         <v>115</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.82500076293945</v>
+        <v>23.97999954223633</v>
       </c>
       <c r="I8" t="n">
-        <v>1.133263342513691</v>
+        <v>1.125938303395065</v>
       </c>
       <c r="J8" t="n">
         <v>115</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.989999771118164</v>
+        <v>5.889999866485596</v>
       </c>
       <c r="I9" t="n">
-        <v>3.338898291187508</v>
+        <v>3.395585815510971</v>
       </c>
       <c r="J9" t="n">
         <v>108</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>7.550000190734863</v>
+        <v>7.5</v>
       </c>
       <c r="I10" t="n">
-        <v>0.7947019666784939</v>
+        <v>0.8</v>
       </c>
       <c r="J10" t="n">
         <v>80</v>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5.179999828338623</v>
+        <v>5.159999847412109</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7335907579013898</v>
+        <v>0.7364341303044438</v>
       </c>
       <c r="J13" t="n">
         <v>59</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>23.82999992370605</v>
+        <v>23.97999954223633</v>
       </c>
       <c r="I14" t="n">
-        <v>1.133025601613219</v>
+        <v>1.125938303395065</v>
       </c>
       <c r="J14" t="n">
         <v>52</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1.957000017166138</v>
+        <v>1.942000031471252</v>
       </c>
       <c r="I15" t="n">
-        <v>2.912621333674779</v>
+        <v>2.935118387038182</v>
       </c>
       <c r="J15" t="n">
         <v>52</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>47.06000137329102</v>
+        <v>45.67499923706055</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1912452132886669</v>
+        <v>0.1970443382667302</v>
       </c>
       <c r="J16" t="n">
         <v>52</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>92.90000152587891</v>
+        <v>92.40000152587891</v>
       </c>
       <c r="I17" t="n">
-        <v>1.4316469086704</v>
+        <v>1.439393915624017</v>
       </c>
       <c r="J17" t="n">
         <v>52</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>5.679999828338623</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I18" t="n">
-        <v>5.281690300468702</v>
+        <v>5.300353499782643</v>
       </c>
       <c r="J18" t="n">
         <v>45</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>2.900000095367432</v>
+        <v>2.960000038146973</v>
       </c>
       <c r="I20" t="n">
-        <v>7.586206647076882</v>
+        <v>7.43243233664703</v>
       </c>
       <c r="J20" t="n">
         <v>10</v>
@@ -1416,10 +1416,10 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>5.179999828338623</v>
+        <v>5.159999847412109</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7335907579013898</v>
+        <v>0.7364341303044438</v>
       </c>
       <c r="J21" t="n">
         <v>3</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>3.019999980926514</v>
+        <v>3.079999923706055</v>
       </c>
       <c r="I23" t="n">
-        <v>4.899635792534151</v>
+        <v>4.804188430691717</v>
       </c>
       <c r="J23" t="n">
         <v>3</v>
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>5.679999828338623</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I24" t="n">
-        <v>4.401408583723919</v>
+        <v>4.416961249818869</v>
       </c>
       <c r="J24" t="n">
         <v>-4</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4.090000152587891</v>
+        <v>4.119999885559082</v>
       </c>
       <c r="I25" t="n">
-        <v>3.422982757382465</v>
+        <v>3.398058346814786</v>
       </c>
       <c r="J25" t="n">
         <v>-11</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>9.822999954223633</v>
+        <v>9.798999786376953</v>
       </c>
       <c r="I26" t="n">
-        <v>2.646849243730342</v>
+        <v>2.653332030494221</v>
       </c>
       <c r="J26" t="n">
         <v>-11</v>
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="H27" t="n">
-        <v>13.65999984741211</v>
+        <v>13.69999980926514</v>
       </c>
       <c r="I27" t="n">
-        <v>4.392386579079429</v>
+        <v>4.379562104768991</v>
       </c>
       <c r="J27" t="n">
         <v>-11</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2.609999895095825</v>
+        <v>2.630000114440918</v>
       </c>
       <c r="I28" t="n">
-        <v>8.429119112739381</v>
+        <v>8.365018647414292</v>
       </c>
       <c r="J28" t="n">
         <v>-11</v>
@@ -1839,10 +1839,10 @@
         </is>
       </c>
       <c r="H30" t="n">
-        <v>6.542500019073486</v>
+        <v>6.599999904632568</v>
       </c>
       <c r="I30" t="n">
-        <v>1.528467706663629</v>
+        <v>1.515151537044865</v>
       </c>
       <c r="J30" t="n">
         <v>-11</v>
@@ -1886,10 +1886,10 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>18.20000076293945</v>
+        <v>18.39999961853027</v>
       </c>
       <c r="I31" t="n">
-        <v>2.06593397933063</v>
+        <v>2.04347830323506</v>
       </c>
       <c r="J31" t="n">
         <v>-11</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>5.650000095367432</v>
+        <v>5.659999847412109</v>
       </c>
       <c r="I33" t="n">
-        <v>2.123893769460125</v>
+        <v>2.120141399913057</v>
       </c>
       <c r="J33" t="n">
         <v>-18</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>2.859999895095825</v>
+        <v>2.880000114440918</v>
       </c>
       <c r="I35" t="n">
-        <v>5.244755437131728</v>
+        <v>5.208333126372769</v>
       </c>
       <c r="J35" t="n">
         <v>-18</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>36.25</v>
+        <v>36.5</v>
       </c>
       <c r="I38" t="n">
-        <v>0.4137931034482759</v>
+        <v>0.410958904109589</v>
       </c>
       <c r="J38" t="n">
         <v>-25</v>
